--- a/config/excel/CfgEnemies.xlsx
+++ b/config/excel/CfgEnemies.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemies" sheetId="1" r:id="Rf7b4bed2185546b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemies" sheetId="1" r:id="Rf492ba54913046cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.###"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
+  </x:numFmts>
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +38,13 @@
       <x:color rgb="FF0000FF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +59,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -63,7 +103,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -88,6 +128,42 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -294,301 +370,413 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="19.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="18" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="18" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="18" t="str">
         <x:v>PrefabAddress</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="18" t="str">
         <x:v>ModelScaleX</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="18" t="str">
         <x:v>ModelScaleY</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="18" t="str">
         <x:v>ModelScaleZ</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="18" t="str">
         <x:v>BaseHealth</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="18" t="str">
         <x:v>HealthPerLevel</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="18" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="18" t="str">
         <x:v>MoveSpeed</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="K1" s="18" t="str">
         <x:v>Radius</x:v>
       </x:c>
-      <x:c r="L1" s="5" t="str">
+      <x:c r="L1" s="18" t="str">
         <x:v>AttackRange</x:v>
       </x:c>
-      <x:c r="M1" s="5" t="str">
+      <x:c r="M1" s="18" t="str">
         <x:v>AggroRange</x:v>
       </x:c>
-      <x:c r="N1" s="5" t="str">
+      <x:c r="N1" s="18" t="str">
         <x:v>SkillID</x:v>
       </x:c>
-      <x:c r="O1" s="5" t="str">
+      <x:c r="O1" s="18" t="str">
         <x:v>ExperienceBase</x:v>
       </x:c>
-      <x:c r="P1" s="5" t="str">
+      <x:c r="P1" s="18" t="str">
         <x:v>ExperiencePerLevel</x:v>
       </x:c>
-      <x:c r="Q1" s="5" t="str">
+      <x:c r="Q1" s="18" t="str">
         <x:v>DropChance</x:v>
       </x:c>
-      <x:c r="R1" s="5" t="str">
+      <x:c r="R1" s="18" t="str">
         <x:v>DropPoolID</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="19" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="19" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="19" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="K2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="L2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="M2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="N2" s="6" t="str">
+      <x:c r="D2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="E2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="F2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="G2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="H2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="I2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="J2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="K2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="L2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="M2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="N2" s="19" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="O2" s="6" t="str">
+      <x:c r="O2" s="19" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="P2" s="6" t="str">
+      <x:c r="P2" s="19" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="Q2" s="6" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="R2" s="6" t="str">
+      <x:c r="Q2" s="19" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="R2" s="19" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="20" t="str">
         <x:v># 敌人编号</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="20" t="str">
         <x:v>敌人名称</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="20" t="str">
         <x:v>敌人模型资源地址</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="20" t="str">
         <x:v>模型X轴缩放</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="20" t="str">
         <x:v>模型Y轴缩放</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="20" t="str">
         <x:v>模型Z轴缩放</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
+      <x:c r="G3" s="20" t="str">
         <x:v>基础生命</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str">
+      <x:c r="H3" s="20" t="str">
         <x:v>每关增加生命</x:v>
       </x:c>
-      <x:c r="I3" s="8" t="str">
+      <x:c r="I3" s="20" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="J3" s="8" t="str">
+      <x:c r="J3" s="20" t="str">
         <x:v>移动速度</x:v>
       </x:c>
-      <x:c r="K3" s="8" t="str">
+      <x:c r="K3" s="20" t="str">
         <x:v>碰撞半径</x:v>
       </x:c>
-      <x:c r="L3" s="8" t="str">
+      <x:c r="L3" s="20" t="str">
         <x:v>攻击范围</x:v>
       </x:c>
-      <x:c r="M3" s="8" t="str">
+      <x:c r="M3" s="20" t="str">
         <x:v>警戒范围</x:v>
       </x:c>
-      <x:c r="N3" s="8" t="str">
+      <x:c r="N3" s="20" t="str">
         <x:v>基础技能编号</x:v>
       </x:c>
-      <x:c r="O3" s="8" t="str">
+      <x:c r="O3" s="20" t="str">
         <x:v>基础击杀经验</x:v>
       </x:c>
-      <x:c r="P3" s="8" t="str">
+      <x:c r="P3" s="20" t="str">
         <x:v>每关增加击杀经验</x:v>
       </x:c>
-      <x:c r="Q3" s="8" t="str">
+      <x:c r="Q3" s="20" t="str">
         <x:v>击杀掉落概率</x:v>
       </x:c>
-      <x:c r="R3" s="8" t="str">
+      <x:c r="R3" s="20" t="str">
         <x:v>掉落池身份</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="3" t="n">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="str">
+      <x:c r="B4" s="16" t="str">
         <x:v>遗迹敌人</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="str">
+      <x:c r="C4" s="16" t="str">
         <x:v>PF_TestEnemy</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="n">
+      <x:c r="D4" s="21" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="n">
+      <x:c r="E4" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="n">
+      <x:c r="F4" s="21" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="n">
+      <x:c r="G4" s="21" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="n">
+      <x:c r="H4" s="21" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="n">
+      <x:c r="I4" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J4" s="3" t="n">
+      <x:c r="J4" s="21" t="n">
         <x:v>2.2</x:v>
       </x:c>
-      <x:c r="K4" s="3" t="n">
+      <x:c r="K4" s="21" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="L4" s="3" t="n">
+      <x:c r="L4" s="21" t="n">
         <x:v>1.6</x:v>
       </x:c>
-      <x:c r="M4" s="3" t="n">
+      <x:c r="M4" s="21" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N4" s="3" t="n">
+      <x:c r="N4" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O4" s="3" t="n">
+      <x:c r="O4" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="n">
+      <x:c r="P4" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q4" s="3" t="n">
+      <x:c r="Q4" s="21" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="R4" s="9" t="str">
+      <x:c r="R4" s="16" t="str">
         <x:v>default</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="3" t="n">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="str">
+      <x:c r="B5" s="16" t="str">
         <x:v>遗迹首领</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>PF_TestBoss</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="n">
+      <x:c r="D5" s="21" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="n">
+      <x:c r="E5" s="21" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="n">
+      <x:c r="F5" s="21" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="n">
+      <x:c r="G5" s="21" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H5" s="3" t="n">
+      <x:c r="H5" s="21" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="n">
+      <x:c r="I5" s="21" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="n">
+      <x:c r="J5" s="21" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="K5" s="3" t="n">
+      <x:c r="K5" s="21" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L5" s="3" t="n">
+      <x:c r="L5" s="21" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="M5" s="3" t="n">
+      <x:c r="M5" s="21" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="n">
+      <x:c r="N5" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O5" s="3" t="n">
+      <x:c r="O5" s="15" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P5" s="3" t="n">
+      <x:c r="P5" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q5" s="3" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="R5" s="9" t="str">
+      <x:c r="Q5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R5" s="16" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>疾行追猎者</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="E6" s="21" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="F6" s="21" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="G6" s="21" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H6" s="21" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I6" s="21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="K6" s="21" t="n">
+        <x:v>0.53</x:v>
+      </x:c>
+      <x:c r="L6" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M6" s="21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N6" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O6" s="15" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P6" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q6" s="21" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="R6" s="16" t="str">
+        <x:v>default</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>重甲破阵者</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E7" s="21" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="F7" s="21" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="G7" s="21" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H7" s="21" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I7" s="21" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J7" s="21" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="K7" s="21" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="L7" s="21" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="M7" s="21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N7" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O7" s="15" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="P7" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q7" s="21" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="R7" s="16" t="str">
         <x:v>default</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgEnemies.xlsx
+++ b/config/excel/CfgEnemies.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemies" sheetId="1" r:id="Rf492ba54913046cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemies" sheetId="1" r:id="R9f28d4a40f7347b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
     <x:numFmt numFmtId="201" formatCode="0.###"/>
     <x:numFmt numFmtId="202" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -43,6 +43,11 @@
       <x:color rgb="FF215E99"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
   <x:fills count="11">
     <x:fill>
@@ -103,7 +108,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -166,6 +171,7 @@
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -780,6 +786,118 @@
         <x:v>default</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="22" t="str">
+        <x:v>双刃游荡者</x:v>
+      </x:c>
+      <x:c r="C8" s="22" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="F8" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="R8" s="22" t="str">
+        <x:v>default</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="22" t="str">
+        <x:v>长柄守卫</x:v>
+      </x:c>
+      <x:c r="C9" s="22" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="F9" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="L9" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="R9" s="22" t="str">
+        <x:v>default</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/config/excel/CfgEnemies.xlsx
+++ b/config/excel/CfgEnemies.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemies" sheetId="1" r:id="R9f28d4a40f7347b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEnemies" sheetId="1" r:id="R040fd604cbbb4bfd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -49,7 +49,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -101,6 +101,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -108,7 +123,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -172,6 +187,14 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -374,528 +397,917 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="18" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="24" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="18" t="str">
+      <x:c r="B1" s="24" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C1" s="18" t="str">
+      <x:c r="C1" s="24" t="str">
         <x:v>PrefabAddress</x:v>
       </x:c>
-      <x:c r="D1" s="18" t="str">
+      <x:c r="D1" s="24" t="str">
         <x:v>ModelScaleX</x:v>
       </x:c>
-      <x:c r="E1" s="18" t="str">
+      <x:c r="E1" s="24" t="str">
         <x:v>ModelScaleY</x:v>
       </x:c>
-      <x:c r="F1" s="18" t="str">
+      <x:c r="F1" s="24" t="str">
         <x:v>ModelScaleZ</x:v>
       </x:c>
-      <x:c r="G1" s="18" t="str">
+      <x:c r="G1" s="24" t="str">
         <x:v>BaseHealth</x:v>
       </x:c>
-      <x:c r="H1" s="18" t="str">
+      <x:c r="H1" s="24" t="str">
         <x:v>HealthPerLevel</x:v>
       </x:c>
-      <x:c r="I1" s="18" t="str">
+      <x:c r="I1" s="24" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="J1" s="18" t="str">
+      <x:c r="J1" s="24" t="str">
         <x:v>MoveSpeed</x:v>
       </x:c>
-      <x:c r="K1" s="18" t="str">
+      <x:c r="K1" s="24" t="str">
         <x:v>Radius</x:v>
       </x:c>
-      <x:c r="L1" s="18" t="str">
+      <x:c r="L1" s="24" t="str">
         <x:v>AttackRange</x:v>
       </x:c>
-      <x:c r="M1" s="18" t="str">
+      <x:c r="M1" s="24" t="str">
         <x:v>AggroRange</x:v>
       </x:c>
-      <x:c r="N1" s="18" t="str">
+      <x:c r="N1" s="24" t="str">
         <x:v>SkillID</x:v>
       </x:c>
-      <x:c r="O1" s="18" t="str">
+      <x:c r="O1" s="24" t="str">
         <x:v>ExperienceBase</x:v>
       </x:c>
-      <x:c r="P1" s="18" t="str">
+      <x:c r="P1" s="24" t="str">
         <x:v>ExperiencePerLevel</x:v>
       </x:c>
-      <x:c r="Q1" s="18" t="str">
-        <x:v>DropChance</x:v>
-      </x:c>
-      <x:c r="R1" s="18" t="str">
-        <x:v>DropPoolID</x:v>
+      <x:c r="Q1" s="24" t="str">
+        <x:v>Role</x:v>
+      </x:c>
+      <x:c r="R1" s="24" t="str">
+        <x:v>Defense</x:v>
+      </x:c>
+      <x:c r="S1" s="24" t="str">
+        <x:v>VulnerableEffectIDs</x:v>
+      </x:c>
+      <x:c r="T1" s="24" t="str">
+        <x:v>VulnerabilityMultiplier</x:v>
+      </x:c>
+      <x:c r="U1" s="24" t="str">
+        <x:v>WeaknessDescription</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="19" t="str">
+      <x:c r="A2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="19" t="str">
+      <x:c r="B2" s="25" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="19" t="str">
+      <x:c r="C2" s="25" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="19" t="str">
+      <x:c r="D2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="E2" s="19" t="str">
+      <x:c r="E2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="F2" s="19" t="str">
+      <x:c r="F2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="G2" s="19" t="str">
+      <x:c r="G2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="H2" s="19" t="str">
+      <x:c r="H2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="I2" s="19" t="str">
+      <x:c r="I2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="J2" s="19" t="str">
+      <x:c r="J2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="K2" s="19" t="str">
+      <x:c r="K2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="L2" s="19" t="str">
+      <x:c r="L2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="M2" s="19" t="str">
+      <x:c r="M2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="N2" s="19" t="str">
+      <x:c r="N2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="O2" s="19" t="str">
+      <x:c r="O2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="P2" s="19" t="str">
+      <x:c r="P2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="Q2" s="19" t="str">
+      <x:c r="Q2" s="25" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="R2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="R2" s="19" t="str">
+      <x:c r="S2" s="25" t="str">
+        <x:v>int[]</x:v>
+      </x:c>
+      <x:c r="T2" s="25" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="U2" s="25" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="56" customHeight="1">
-      <x:c r="A3" s="20" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="27" t="str">
         <x:v># 敌人编号</x:v>
       </x:c>
-      <x:c r="B3" s="20" t="str">
+      <x:c r="B3" s="27" t="str">
         <x:v>敌人名称</x:v>
       </x:c>
-      <x:c r="C3" s="20" t="str">
+      <x:c r="C3" s="27" t="str">
         <x:v>敌人模型资源地址</x:v>
       </x:c>
-      <x:c r="D3" s="20" t="str">
+      <x:c r="D3" s="27" t="str">
         <x:v>模型X轴缩放</x:v>
       </x:c>
-      <x:c r="E3" s="20" t="str">
+      <x:c r="E3" s="27" t="str">
         <x:v>模型Y轴缩放</x:v>
       </x:c>
-      <x:c r="F3" s="20" t="str">
+      <x:c r="F3" s="27" t="str">
         <x:v>模型Z轴缩放</x:v>
       </x:c>
-      <x:c r="G3" s="20" t="str">
+      <x:c r="G3" s="27" t="str">
         <x:v>基础生命</x:v>
       </x:c>
-      <x:c r="H3" s="20" t="str">
+      <x:c r="H3" s="27" t="str">
         <x:v>每关增加生命</x:v>
       </x:c>
-      <x:c r="I3" s="20" t="str">
+      <x:c r="I3" s="27" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="J3" s="20" t="str">
+      <x:c r="J3" s="27" t="str">
         <x:v>移动速度</x:v>
       </x:c>
-      <x:c r="K3" s="20" t="str">
+      <x:c r="K3" s="27" t="str">
         <x:v>碰撞半径</x:v>
       </x:c>
-      <x:c r="L3" s="20" t="str">
+      <x:c r="L3" s="27" t="str">
         <x:v>攻击范围</x:v>
       </x:c>
-      <x:c r="M3" s="20" t="str">
+      <x:c r="M3" s="27" t="str">
         <x:v>警戒范围</x:v>
       </x:c>
-      <x:c r="N3" s="20" t="str">
+      <x:c r="N3" s="27" t="str">
         <x:v>基础技能编号</x:v>
       </x:c>
-      <x:c r="O3" s="20" t="str">
+      <x:c r="O3" s="27" t="str">
         <x:v>基础击杀经验</x:v>
       </x:c>
-      <x:c r="P3" s="20" t="str">
+      <x:c r="P3" s="27" t="str">
         <x:v>每关增加击杀经验</x:v>
       </x:c>
-      <x:c r="Q3" s="20" t="str">
-        <x:v>击杀掉落概率</x:v>
-      </x:c>
-      <x:c r="R3" s="20" t="str">
-        <x:v>掉落池身份</x:v>
+      <x:c r="Q3" s="27" t="str">
+        <x:v>敌人类别：0普通1精英2首领</x:v>
+      </x:c>
+      <x:c r="R3" s="27" t="str">
+        <x:v>防御值</x:v>
+      </x:c>
+      <x:c r="S3" s="27" t="str">
+        <x:v>额外承伤的伤害事件DefinitionID</x:v>
+      </x:c>
+      <x:c r="T3" s="27" t="str">
+        <x:v>对应伤害倍率</x:v>
+      </x:c>
+      <x:c r="U3" s="27" t="str">
+        <x:v>玩家可见战斗特点与弱点</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="36" customHeight="1">
-      <x:c r="A4" s="15" t="n">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="28" t="str">
         <x:v>遗迹敌人</x:v>
       </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="C4" s="28" t="str">
         <x:v>PF_TestEnemy</x:v>
       </x:c>
-      <x:c r="D4" s="21" t="n">
+      <x:c r="D4" s="28" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="E4" s="21" t="n">
+      <x:c r="E4" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F4" s="21" t="n">
+      <x:c r="F4" s="28" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="G4" s="21" t="n">
+      <x:c r="G4" s="28" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H4" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I4" s="21" t="n">
+      <x:c r="H4" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I4" s="28" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J4" s="21" t="n">
+      <x:c r="J4" s="28" t="n">
         <x:v>2.2</x:v>
       </x:c>
-      <x:c r="K4" s="21" t="n">
+      <x:c r="K4" s="28" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="L4" s="21" t="n">
+      <x:c r="L4" s="28" t="n">
         <x:v>1.6</x:v>
       </x:c>
-      <x:c r="M4" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N4" s="15" t="n">
+      <x:c r="M4" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N4" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O4" s="15" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P4" s="15" t="n">
+      <x:c r="O4" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P4" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q4" s="21" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="R4" s="16" t="str">
-        <x:v>default</x:v>
-      </x:c>
+      <x:c r="Q4" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R4" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S4" s="28" t="str"/>
+      <x:c r="T4" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U4" s="28" t="str"/>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
-      <x:c r="A5" s="15" t="n">
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>遗迹首领</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="B5" s="28" t="str">
+        <x:v>遗迹守门者</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
         <x:v>PF_TestBoss</x:v>
       </x:c>
-      <x:c r="D5" s="21" t="n">
+      <x:c r="D5" s="28" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="E5" s="21" t="n">
+      <x:c r="E5" s="28" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="F5" s="21" t="n">
+      <x:c r="F5" s="28" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="G5" s="21" t="n">
+      <x:c r="G5" s="28" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I5" s="28" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J5" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K5" s="28" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L5" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M5" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N5" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O5" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P5" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q5" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R5" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" s="28" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T5" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U5" s="28" t="str">
+        <x:v>环形重击前离开范围；流血额外有效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="28" t="str">
+        <x:v>疾行追猎者</x:v>
+      </x:c>
+      <x:c r="C6" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D6" s="28" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="E6" s="28" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="F6" s="28" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="G6" s="28" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H6" s="28" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I6" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J6" s="28" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="K6" s="28" t="n">
+        <x:v>0.53</x:v>
+      </x:c>
+      <x:c r="L6" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M6" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N6" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O6" s="28" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P6" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q6" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="28" t="str"/>
+      <x:c r="T6" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U6" s="28" t="str"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="str">
+        <x:v>重甲破阵者</x:v>
+      </x:c>
+      <x:c r="C7" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D7" s="28" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="G7" s="28" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H7" s="28" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I7" s="28" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J7" s="28" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="K7" s="28" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="L7" s="28" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="M7" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N7" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O7" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="P7" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q7" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="28" t="str"/>
+      <x:c r="T7" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U7" s="28" t="str"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B8" s="28" t="str">
+        <x:v>双刃游荡者</x:v>
+      </x:c>
+      <x:c r="C8" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D8" s="28" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="E8" s="28" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="F8" s="28" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="G8" s="28" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H8" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="28" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J8" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K8" s="28" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="L8" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="M8" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N8" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O8" s="28" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P8" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q8" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="28" t="str"/>
+      <x:c r="T8" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U8" s="28" t="str"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B9" s="28" t="str">
+        <x:v>长柄守卫</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G9" s="28" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H9" s="28" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I9" s="28" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J9" s="28" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="K9" s="28" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="L9" s="28" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="M9" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N9" s="28" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O9" s="28" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P9" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q9" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="28" t="str"/>
+      <x:c r="T9" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U9" s="28" t="str"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B10" s="28" t="str">
+        <x:v>精英·疾行追猎者</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="F10" s="28" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="G10" s="28" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H10" s="28" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I10" s="28" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J10" s="28" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="K10" s="28" t="n">
+        <x:v>0.53</x:v>
+      </x:c>
+      <x:c r="L10" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M10" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N10" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O10" s="28" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="P10" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q10" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R10" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="28" t="str">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="T10" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U10" s="28" t="str">
+        <x:v>移速快；反击伤害对其额外有效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B11" s="28" t="str">
+        <x:v>精英·重甲破阵者</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H11" s="28" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I11" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J11" s="28" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="K11" s="28" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="L11" s="28" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="M11" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N11" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O11" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="P11" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q11" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R11" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="28" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T11" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U11" s="28" t="str">
+        <x:v>攻击缓慢；流血伤害对其额外有效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="28" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B12" s="28" t="str">
+        <x:v>精英·双刃守卫</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="str">
+        <x:v>PF_TestEnemy</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H5" s="21" t="n">
+      <x:c r="H12" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I12" s="28" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J12" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K12" s="28" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="L12" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="M12" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N12" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O12" s="28" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P12" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q12" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R12" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="28" t="str">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="T12" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U12" s="28" t="str">
+        <x:v>双段近战；暴击追伤对其额外有效。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B13" s="28" t="str">
+        <x:v>庭院双刃统领</x:v>
+      </x:c>
+      <x:c r="C13" s="28" t="str">
+        <x:v>PF_TestBoss</x:v>
+      </x:c>
+      <x:c r="D13" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="n">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="H13" s="28" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I5" s="21" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="J5" s="21" t="n">
+      <x:c r="I13" s="28" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J13" s="28" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="K5" s="21" t="n">
+      <x:c r="K13" s="28" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L5" s="21" t="n">
+      <x:c r="L13" s="28" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="M5" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N5" s="15" t="n">
+      <x:c r="M13" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N13" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O5" s="15" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P5" s="15" t="n">
+      <x:c r="O13" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P13" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="Q5" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R5" s="16" t="str">
-        <x:v>boss</x:v>
+      <x:c r="Q13" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R13" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="28" t="str">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="T13" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U13" s="28" t="str">
+        <x:v>中距离追击与近身爆发；暴击追伤额外有效。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="36" customHeight="1">
-      <x:c r="A6" s="15" t="n">
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="28" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B14" s="28" t="str">
+        <x:v>遗迹核心守望者</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="str">
+        <x:v>PF_TestBoss</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="F14" s="28" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H14" s="28" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I14" s="28" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J14" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K14" s="28" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L14" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M14" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N14" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
-        <x:v>疾行追猎者</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="str">
-        <x:v>PF_TestEnemy</x:v>
-      </x:c>
-      <x:c r="D6" s="21" t="n">
-        <x:v>1.05</x:v>
-      </x:c>
-      <x:c r="E6" s="21" t="n">
-        <x:v>1.05</x:v>
-      </x:c>
-      <x:c r="F6" s="21" t="n">
-        <x:v>1.05</x:v>
-      </x:c>
-      <x:c r="G6" s="21" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="H6" s="21" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I6" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J6" s="21" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="K6" s="21" t="n">
-        <x:v>0.53</x:v>
-      </x:c>
-      <x:c r="L6" s="21" t="n">
+      <x:c r="O14" s="28" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P14" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q14" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M6" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N6" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O6" s="15" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="P6" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="Q6" s="21" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="R6" s="16" t="str">
-        <x:v>default</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1">
-      <x:c r="A7" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="16" t="str">
-        <x:v>重甲破阵者</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="str">
-        <x:v>PF_TestEnemy</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="n">
-        <x:v>1.3</x:v>
-      </x:c>
-      <x:c r="E7" s="21" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="n">
-        <x:v>1.3</x:v>
-      </x:c>
-      <x:c r="G7" s="21" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="H7" s="21" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I7" s="21" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J7" s="21" t="n">
-        <x:v>1.35</x:v>
-      </x:c>
-      <x:c r="K7" s="21" t="n">
-        <x:v>0.67</x:v>
-      </x:c>
-      <x:c r="L7" s="21" t="n">
-        <x:v>2.4</x:v>
-      </x:c>
-      <x:c r="M7" s="21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N7" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="O7" s="15" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="P7" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Q7" s="21" t="n">
-        <x:v>0.65</x:v>
-      </x:c>
-      <x:c r="R7" s="16" t="str">
-        <x:v>default</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="36" customHeight="1">
-      <x:c r="A8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="22" t="str">
-        <x:v>双刃游荡者</x:v>
-      </x:c>
-      <x:c r="C8" s="22" t="str">
-        <x:v>PF_TestEnemy</x:v>
-      </x:c>
-      <x:c r="D8" t="n">
-        <x:v>0.76</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
-        <x:v>0.9</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>0.76</x:v>
-      </x:c>
-      <x:c r="G8" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I8" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="J8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K8" t="n">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="L8" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="M8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="O8" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="Q8" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="R8" s="22" t="str">
-        <x:v>default</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="36" customHeight="1">
-      <x:c r="A9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="22" t="str">
-        <x:v>长柄守卫</x:v>
-      </x:c>
-      <x:c r="C9" s="22" t="str">
-        <x:v>PF_TestEnemy</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I9" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J9" t="n">
-        <x:v>1.7</x:v>
-      </x:c>
-      <x:c r="K9" t="n">
-        <x:v>0.55</x:v>
-      </x:c>
-      <x:c r="L9" t="n">
-        <x:v>3.7</x:v>
-      </x:c>
-      <x:c r="M9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="O9" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="P9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Q9" t="n">
-        <x:v>0.65</x:v>
-      </x:c>
-      <x:c r="R9" s="22" t="str">
-        <x:v>default</x:v>
+      <x:c r="R14" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="28" t="str">
+        <x:v>5,1002,1004</x:v>
+      </x:c>
+      <x:c r="T14" s="28" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="U14" s="28" t="str">
+        <x:v>后半程冲锋；流血、暴击追伤、反击均有优势。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
